--- a/entregas/plano-contingencia-agua/planilha-mestre/planilha-mestre.xlsx
+++ b/entregas/plano-contingencia-agua/planilha-mestre/planilha-mestre.xlsx
@@ -716,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Cenários</t>
@@ -724,7 +724,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>1 Contaminação cruzada · 2 Falta de água · 3 Água fora do padrão · 4 Vazamento e alagamento · 5 Falha de bomba ou energia · 6 Incêndio com reserva indisponível · 7 Refluxo de esgoto · 8 Falha do tratamento químico · 9 Contaminação do reservatório · T Comunicação de crise. Os procedimentos dos cenários 1, 2 e 5 estão em entregas/plano-contingencia-agua/cenarios/.</t>
+          <t>1 Contaminação cruzada · 2 Falta de água · 3 Água fora do padrão · 4 Vazamento e alagamento · 5 Falha de bomba ou energia · 6 Incêndio com reserva indisponível · 7 Refluxo de esgoto · 8 Falha do tratamento químico · 9 Contaminação do reservatório · T Comunicação de crise. Os procedimentos dos cenários 1, 2, 3, 5, 8 e 9 estão em entregas/plano-contingencia-agua/cenarios/; os checklists de ronda e do relatório mensal dos fornecedores estão em .../rotinas/.</t>
         </is>
       </c>
     </row>

--- a/entregas/plano-contingencia-agua/planilha-mestre/planilha-mestre.xlsx
+++ b/entregas/plano-contingencia-agua/planilha-mestre/planilha-mestre.xlsx
@@ -716,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="75" customHeight="1">
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Cenários</t>
@@ -724,7 +724,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>1 Contaminação cruzada · 2 Falta de água · 3 Água fora do padrão · 4 Vazamento e alagamento · 5 Falha de bomba ou energia · 6 Incêndio com reserva indisponível · 7 Refluxo de esgoto · 8 Falha do tratamento químico · 9 Contaminação do reservatório · T Comunicação de crise. Os procedimentos dos cenários 1, 2, 3, 5, 8 e 9 estão em entregas/plano-contingencia-agua/cenarios/; os checklists de ronda e do relatório mensal dos fornecedores estão em .../rotinas/.</t>
+          <t>1 Contaminação cruzada · 2 Falta de água · 3 Água fora do padrão · 4 Vazamento e alagamento · 5 Falha de bomba ou energia · 6 Incêndio com reserva indisponível · 7 Refluxo de esgoto · 8 Falha do tratamento químico · 9 Contaminação do reservatório · T Comunicação de crise. Os procedimentos dos cenários 1 a 9 (o T, comunicação de crise, ainda não existe) estão em entregas/plano-contingencia-agua/cenarios/; os checklists de ronda e do relatório mensal dos fornecedores estão em .../rotinas/.</t>
         </is>
       </c>
     </row>

--- a/entregas/plano-contingencia-agua/planilha-mestre/planilha-mestre.xlsx
+++ b/entregas/plano-contingencia-agua/planilha-mestre/planilha-mestre.xlsx
@@ -724,7 +724,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>1 Contaminação cruzada · 2 Falta de água · 3 Água fora do padrão · 4 Vazamento e alagamento · 5 Falha de bomba ou energia · 6 Incêndio com reserva indisponível · 7 Refluxo de esgoto · 8 Falha do tratamento químico · 9 Contaminação do reservatório · T Comunicação de crise. Os procedimentos dos cenários 1 a 9 (o T, comunicação de crise, ainda não existe) estão em entregas/plano-contingencia-agua/cenarios/; os checklists de ronda e do relatório mensal dos fornecedores estão em .../rotinas/.</t>
+          <t>1 Contaminação cruzada · 2 Falta de água · 3 Água fora do padrão · 4 Vazamento e alagamento · 5 Falha de bomba ou energia · 6 Incêndio com reserva indisponível · 7 Refluxo de esgoto · 8 Falha do tratamento químico · 9 Contaminação do reservatório · T Comunicação de crise. Os procedimentos dos cenários 1 a 9 e do T (comunicação de crise) estão em entregas/plano-contingencia-agua/cenarios/; os checklists de ronda e do relatório mensal dos fornecedores estão em .../rotinas/.</t>
         </is>
       </c>
     </row>

--- a/entregas/plano-contingencia-agua/planilha-mestre/planilha-mestre.xlsx
+++ b/entregas/plano-contingencia-agua/planilha-mestre/planilha-mestre.xlsx
@@ -1873,7 +1873,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Disque-Intoxicação (confirmar número vigente)</t>
+          <t>Centro de informação toxicológica (telefone a confirmar)</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
@@ -1886,7 +1886,7 @@
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Anvisa: 0800 722 6001 — conferir se continua vigente antes de usar</t>
+          <t>Preencher com o telefone do centro de informação toxicológica (confirmar o número vigente)</t>
         </is>
       </c>
     </row>
